--- a/docs/perechen-otchetov/obrazcy/ФО-59.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-59.xlsx
@@ -7,18 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Образец" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ФО-59" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Параметры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Описание" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'ФО-59'!$5:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +32,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
@@ -50,12 +81,22 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -89,41 +130,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,11 +571,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -502,442 +584,1027 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ОАО «Государственный финансовый холдинг»</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>ФО-59</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
           <t>Кредитный риск портфеля</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>за III квартал 2026 года (с 01.07.2026 по 01.10.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>за период с 01.09.2026 по 30.09.2026, тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Единица</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>На начало квартала</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>На конец квартала</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Изменение</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Остаток основной суммы портфеля</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>сом</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>43507500</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>39482500</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>-4025000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Размер и качество портфеля</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>На начало периода</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>На конец периода</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Изменение за период</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Кредитов в портфеле</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Заёмщиков с кредитами в состоянии «Действует»</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="E7" s="8" t="n">
+      <c r="C9" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Кредитов в состоянии «Действует»</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>вступили в действие</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>закрыты (погашены, списаны, расторгнуты)</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="11" t="n">
         <v>-2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Остаток основного долга</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>75638</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>75037.5</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-600.5</v>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>освоено</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="18" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>погашено</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="18" t="n">
+        <v>-1467</v>
+      </c>
+    </row>
+    <row r="16" ht="13" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>списано</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="18" t="n">
+        <v>-750</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>курсовая разница</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="18" t="n">
+        <v>116.5</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Не освоено по договорам в состоянии «Действует» и «Зарегистрирован»</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Просроченная задолженность</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>сом</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>3859000</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>4560750</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>701750</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Доля просроченной задолженности в остатке портфеля</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Кредитов с просрочкой</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>появилась просрочка</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>просрочки не стало (погашена, списана, кредит закрыт)</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Просроченная задолженность — основная сумма, проценты, штрафы</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>9142.097634457143</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>10347.215</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>1205.117365542857</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Остаток основного долга кредитов с просрочкой</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>40189.6</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>41417</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>1227.400000000001</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>просрочка до 180 дней (средний риск)</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>23591.6</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>12842</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>-10749.6</v>
+      </c>
+    </row>
+    <row r="26" ht="13" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>просрочка более 180 дней (высокий риск)</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>16598</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>28575</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>11977</v>
+      </c>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Доля остатка кредитов с просрочкой в остатке основного долга</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Средняя просрочка по кредитам с просрочкой</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="C27" s="19" t="n">
+        <v>53.13413892487903</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>55.19506913210061</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>2.060930207221588</v>
+      </c>
+    </row>
+    <row r="28" ht="13" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Средняя длительность просрочки</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>дн.</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
-        <v>136</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>180.1</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>44.1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Доля проблемных кредитов (ФО-28)</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="C28" s="19" t="n">
+        <v>158.6153846153846</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>149.5384615384615</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>-9.076923076923066</v>
+      </c>
+    </row>
+    <row r="29" ht="13" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Группы платёжеспособности</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="13" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Остаток основного долга заёмщиков группы 1.1</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>33598.4</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>31820.5</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>-1777.900000000001</v>
+      </c>
+    </row>
+    <row r="31" ht="13" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Остаток основного долга проблемных кредитов (группа не 1.1)</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>42039.6</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>43217</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>1177.400000000001</v>
+      </c>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>группа 1.2</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>35439.6</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>13242</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>-22197.6</v>
+      </c>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>группа 2.1–2.3</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>27775</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>21175</v>
+      </c>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>группа 3.1–3.2</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>группа 4</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Проблемных заёмщиков</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Доля проблемных кредитов в остатке основного долга</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Структура по группам платёжеспособности</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Остаток в группе 1.1 (без просроченной задолженности)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>сом</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>28537500</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>24512500</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>-4025000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Остаток в группе 1.2 (платят не в полном объёме)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>сом</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>7620000</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>8370000</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Остаток в группах 2.1–2.3 (взыскание, исполнительные документы, банкротство)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>сом</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>6600000</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>-2200000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Остаток в группах 3.1 и ниже (процедура банкротства, безнадёжные)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>сом</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>750000</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>2200000</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>1450000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="C37" s="19" t="n">
+        <v>55.57999947116529</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>57.59386973180077</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>2.013870260635478</v>
+      </c>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Концентрация</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Доля пяти крупнейших заёмщиков в остатке портфеля</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Доля крупнейшего заёмщика в остатке основного долга</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Остаток крупнейшего заёмщика</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>сом</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>6375000</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>-1275000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="C39" s="19" t="n">
+        <v>20.44474999338956</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>20.65633849741796</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>0.2115885040283949</v>
+      </c>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Доля пяти крупнейших заёмщиков в остатке основного долга</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>54.41762077262752</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>54.17957687822755</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>-0.238043894399965</v>
+      </c>
+    </row>
+    <row r="41" ht="13" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Пять крупнейших заёмщиков на конец периода, остаток основного долга</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>ОсОО «Кемин-Курулуш»</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>15464</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>15500</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>ОсОО «Кербен-Жибек»</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>7848</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>7875</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>ОсОО «Ала-Арча Энерго»</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>7286.4</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>7308</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>21.60000000000036</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>ОсОО «Ак-Дан»</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>5330</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>5100</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>-230</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>ОсОО «Сулайман-Тоо Трейд»</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>4857.6</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>4872</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>14.39999999999964</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Обеспеченность залогом</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Кредитов, остаток которых больше оценки залога</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Остаток основного долга кредитов с залогом</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>8250</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>7650</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>обеспечен по порогу</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>7100</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>-3500</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>не обеспечен — залога меньше порога</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>4050</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Остаток основного долга кредитов без залога</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>67388</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>67387.5</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Недостаёт залога до порога</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>330</v>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>785</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Реструктуризация</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Реструктурированных кредитов</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Остаток основного долга реструктурированных кредитов</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Обращений о реструктуризации в работе</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Остаток, не покрытый оценкой залога</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>сом</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>750000</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>400000</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>-350000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Реструктуризация</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Реструктурированных кредитов</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
+      <c r="D56" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Остаток реструктурированных кредитов</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>сом</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>1800000</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="7">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Arial"&amp;8 ФО-59 · сформировал Касымова Д. Т. 06.10.2026 12:00 · Страница &amp;P из &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -947,7 +1614,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Параметры отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>ФО-59 «Кредитный риск портфеля за период»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>01.09.2026 – 30.09.2026 (выбран; по умолчанию — прошлый квартал)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>На начало и на конец</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>остатки, группы, залог — на конец 31.08.2026 и на конец 30.09.2026; просроченная задолженность, дни и длительность просрочки — на 01.09.2026 и 01.10.2026, как ФО-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Что попадает</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>кредиты в состоянии «Действует» на каждую из дат, включая кредиты с остатком основного долга 0,00; в «Не освоено по договорам» — и кредиты «Зарегистрирован»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Отбор</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Единица</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>тыс. сом</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>Курсы валют</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>на начало — на 31.08.2026: USD 87,20000, EUR 101,20000; на конец — на 30.09.2026: USD 87,50000, EUR 101,50000; изменение остатка включает курсовую разницу</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Период закрыт</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>сентябрь 2026 — закрыт 05.10.2026; исправлений после закрытия нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Рассчитан</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>06.10.2026 09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Сформировал</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Касымова Д. Т.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Округление</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>В ячейках — точные значения, на экране и в печати — тыс. сом с двумя знаками, доли и длительность — с одним. Итоги, доли и изменения считаются по точным значениям, поэтому сумма округлённых строк может отличаться от итога на 0,01, изменение доли — на 0,1.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -956,383 +1781,450 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ФО-59 «Кредитный риск портфеля» — карточка</t>
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>ФО-59 «Кредитный риск портфеля за период» — карточка</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>ФО-59</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Кредитный риск портфеля</t>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Кредитный риск портфеля за период</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Часть</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Модуль</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Риски</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Получатель</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Правление</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Язык</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10; Порядок №41 пп. 11, 14–65; ТЗ 19 §15</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Образец-основа</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="195" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Правлению — состояние и тенденции кредитного риска по портфелю бюджетных кредитов: качество, структура по группам платёжеспособности, концентрация, обеспеченность, реструктуризация. Отдел риск-менеджмента представляет информацию не реже раза в квартал (Политика №28 п. 5.4.4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Правлению — обзор кредитного риска портфеля бюджетных кредитов не реже раза в квартал (Политика №28 п. 5.4.4): размер и движение портфеля, просроченная задолженность и её тяжесть, состав по группам платёжеспособности, концентрация на крупнейших заёмщиках, обеспеченность залогом и реструктуризация — на начало и на конец периода с изменением. Готовит служба риск-менеджмента и контроля; отчёт — фактическая часть её доклада, оценку, рекомендации и меры снижения риска служба пишет Правлению сама, вне отчёта. Каждый показатель считается по правилу своего отчёта: просроченная задолженность, дни просрочки и категория риска — ФО-01, длительность просрочки — ФО-27, группы и доля проблемных кредитов — ФО-24 и ФО-28, неосвоенная часть договоров — ФО-08, обеспеченность — ФО-14 (вид «Обеспеченность кредитов залогом»), реструктуризация — ФО-57 и ФО-10, движение остатка — освоено ФО-56, погашено ФО-04, списано ФО-11, курсовая разница ФО-53. Свои числа отчёта — концентрация, разложение изменений и сравнение двух дат; по департаментам и кураторам те же доли дают ФО-28 и ФО-01. Резерв и ожидаемые кредитные убытки система не считает (ТЗ 19 §15): входные данные для их расчёта — ФО-57. В старой системе такого отчёта не было.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>За квартал: сравнение начала и конца квартала; по требованию. Формируется по окончании квартала. Начало квартала — данные на конец дня перед первым числом, конец — на конец дня перед первым числом следующего месяца.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>За период: ежеквартально после закрытия последнего месяца квартала и по требованию; по умолчанию — прошлый квартал. Можно выбрать любой период (месяц, полугодие, год). На начало — данные на конец дня перед началом периода, на конец — на конец последнего дня периода; просроченная задолженность, дни и длительность просрочки — на следующий день, как ФО-01 (за III квартал — на 01.07 и 01.10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="105" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>• Квартал — прошлый
-• Единица — сом</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="75" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>• Период — прошлый квартал; можно выбрать любой
+• Единица — тыс. сом (можно выбрать «сом»)
+• Отбор — департамент, валюта, кредитная программа, вид лица; все показатели, в том числе доли и пятёрка крупнейших заёмщиков, считаются по отобранным кредитам
+• Разрезов нет: строка — показатель, состав и порядок показателей заданы формой</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="240" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Группа показателей → показатель. Сверху строка с остатком основной суммы портфеля. Группы и показатели идут в порядке образца; сортировки нет. Все показатели считаются по кредитам в состояниях «Зарегистрирован» и «Действует» на начало и конец квартала. Не входят: резерв и ожидаемые кредитные убытки (расчёт у службы рисков вне системы), показатели по отраслям и связанным лицам, уровень возвратности кредитов.</t>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Строка — показатель портфеля; показатели сгруппированы в шесть разделов, строка раздела залита: портфель, просроченная задолженность, группы платёжеспособности, концентрация, обеспеченность залогом, реструктуризация. Строки ИТОГО нет. Строки ниже показателя — его состав (группы, сроки просрочки, обеспеченность) или разложение изменения за период (освоено − погашено − списано + курсовая разница; вступили в действие − закрыты; появилась просрочка − просрочки не стало): их сумма равна строке выше в своей колонке. База — кредиты в состоянии «Действует» на каждую из дат, включая кредит с остатком основного долга 0,00 (остались проценты или штрафы); кредит «Зарегистрирован» без освоения входит только в «Не освоено по договорам» (= ФО-08). Кредит, закрытый в периоде, есть на начало и нет на конец, вступивший в действие — наоборот; после перевода долга кредит — у нового заёмщика. Пятёрка крупнейших заёмщиков — по остатку основного долга всех их кредитов на конец периода, с остатком тех же заёмщиков на начало; доли крупнейших на каждую дату — по своей пятёрке этой даты. Формат числа — по единице строки: шт. — целые, тыс. сом — 2 знака, % и дн. — 1 знак; изменение доли — в процентных пунктах. Не входят: резерв, стадии и ожидаемые кредитные убытки (служба рисков, вне системы), возвратность кредитов (в системе не определена), концентрация по отраслям (разрезом «Отрасль» в ФО-02), кредиты связанным лицам (в системе таких сведений нет).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>Разрезы</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>по умолчанию: Раздел показателей → показатель; можно выбрать: Раздел показателей</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Если строк нет</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Действующих кредитов на начало и на конец периода по условиям отбора нет: счётчики и суммы — 0,00, доли и длительность — пусто.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Выгрузка</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>xlsx, pdf</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Новая форма: в старой системе отчёта не было (Политика №28 п. 5.4.4 — отчёт отдела риск-менеджмента Правлению не реже раза в квартал). Строка — показатель портфеля на начало и конец периода (по умолчанию — квартал) с изменением, в шести разделах: портфель и движение остатка, просроченная задолженность (кредиты, сумма, остаток кредитов с просрочкой до и более 180 дней, доля, средняя длительность), группы платёжеспособности и доля проблемных, концентрация (крупнейший заёмщик, пятёрка крупнейших), обеспеченность залогом, реструктуризация; каждый показатель — по правилу своего отчёта (ФО-01, 08, 10, 14, 24, 27, 28, 57). Резерв и ожидаемые кредитные убытки — у службы рисков вне системы (входные данные — ФО-57)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>⚠ Нужно от заказчика</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Состав показателей — от службы рисков</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Колонки</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>Колонка</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Общая шапка</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>Что в ней</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr"/>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>наименование группы или показателя. Расчёт: «Просроченная задолженность» — как в ФО-01; «Доля просроченной задолженности» — просроченная / остаток портфеля; «Средняя просрочка» — как в ФО-27 (принято: среднее по кредитам с просрочкой); «Доля проблемных кредитов» — как в ФО-28 (принято: группа не 1.1); «Остаток в группе» — остаток основной суммы кредитов заёмщиков группы на дату, названия групп по Инструкции №14; «2.1–2.3» и «3.1 и ниже» — по группе заёмщика на дату; «Доля пяти крупнейших заёмщиков» — сумма остатков основной суммы пяти заёмщиков с наибольшим остатком по всем их кредитам / остаток портфеля; «Остаток крупнейшего заёмщика» — то же для одного; «Кредитов, остаток которых больше оценки залога» — остаток основной суммы кредита больше суммы оценок его залога (принято: основа — остаток основной суммы, не вся задолженность); «Остаток, не покрытый оценкой залога» — сумма положительных разностей «остаток основной суммы − оценка залога» по кредитам; «Реструктурированных» — кредиты с вступившим в силу дополнительным соглашением о реструктуризации (как в ФО-57)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr"/>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>раздел, показатель или его часть — по уровню строки; в пятёрке крупнейших — наименование заёмщика. Расчёт: «Остаток основного долга» — по кредитам «Действует», как ФО-28; «освоено», «погашено», «списано», «курсовая разница» — основной долг за период, как ФО-56, ФО-04, ФО-11, ФО-53; «Не освоено» — сумма договора минус освоено, как ФО-08; «Кредитов с просрочкой», «Просроченная задолженность», «Остаток основного долга кредитов с просрочкой» и сроки «до 180 / более 180 дней» — как ФО-01 (категории риска средний и высокий, Порядок №41 п. 11); «Средняя длительность просрочки» — средняя длительность тянущихся эпизодов просрочки на дату, как ФО-27; «Проблемный кредит» — кредит заёмщика группы не 1.1 на дату, как ФО-28, группы — хранимое значение классификатора на дату; «Доля крупнейшего» и «Доля пяти крупнейших» — остаток основного долга по всем кредитам заёмщика (пяти заёмщиков с наибольшим остатком) ÷ остаток портфеля; «Обеспеченность» — по правилу вида «Обеспеченность кредитов залогом» ФО-14: залоговая стоимость отнесённых предметов против порога 120 % или 150 %, «без залога» — к кредиту не отнесён ни один предмет по зарегистрированному договору залога; «Реструктурированный» — кредит, условия которого изменены дополнительным соглашением о реструктуризации, как ФО-57; «Обращений в работе» — как ФО-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>Единица</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr"/>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>шт., сом, %, дн.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>На начало квартала</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr"/>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>значение на первое число первого месяца квартала</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>На конец квартала</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr"/>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>значение на первое число месяца, следующего за кварталом</t>
+      <c r="B24" s="26" t="inlineStr"/>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>шт., тыс. сом (сом — по параметру «Единица»), %, дн.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Изменение</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr"/>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>конец − начало; для процентов — в процентных пунктах</t>
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>На начало периода</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr"/>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>значение на конец дня перед началом периода; просроченная задолженность, дни и длительность — на первое число периода, как ФО-01; у строки разложения изменения — пусто</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>На конец периода</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr"/>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>значение на конец последнего дня периода; просроченная задолженность, дни и длительность — на следующий день; у строки разложения изменения — пусто</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>Изменение за период</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr"/>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>на конец − на начало; у доли — в процентных пунктах; у строки разложения — её вклад в изменение строки выше со знаком: освоено и вступили в действие «+», погашено, списано, закрыты «−»</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Правила проверки</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>„Остаток основной суммы портфеля“ на конец квартала = ИТОГО ФО-26 на ту же дату (39 482 500,00); „Просроченная задолженность“ = ИТОГО ФО-01 (4 560 750,00); кредитов 17.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026 (период выбран; по умолчанию — квартал, в наборе состояние известно на 31.08 и 30.09): заёмщиков 22 → 21, кредитов «Действует» 25 → 24 = 25 + 1 (КЗ-17 вступил в действие 15.09.2026) − 2 (КЗ-08 списан 17.09.2026, КЗ-15 погашен 18.09.2026) — как ФО-58; на конец = ФО-28 (21 заёмщик, 24 кредита).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="75" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>„Доля проблемных кредитов“ = итог ФО-28 (37,9 %), „Средняя просрочка“ = итог ФО-27 (180,1) на ту же дату.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>Остаток основного долга: на начало 75 638,000 = ФО-24 на 31.08.2026, на конец 75 037,500 = ФО-28 = ФО-25 = ФО-24 на 30.09.2026; изменение −600,500 = освоено 1 500,000 (ФО-56, КЗ-17) − погашено 1 467,000 (ФО-04) − списано 750,000 (ФО-11, КЗ-08) + курсовая разница 116,500 (ФО-53). Не освоено: 4 400,000 (КЗ-12 1 500,000, КЗ-18 900,000, КЗ-26 2 000,000) → 3 500,000 = ФО-08 (КЗ-18 расторгнут 10.09.2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Остатки по группам платёжеспособности в сумме равны остатку портфеля; группа каждого заёмщика совпадает с ФО-24: на конец квартала 2.1–2.3 — КЗ-05 и КЗ-10 (4 400 000,00), 3.1 и ниже — КЗ-19 (2 200 000,00).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>Просрочка на 01.10.2026 = ИТОГО ФО-01: 13 кредитов, просроченная задолженность 10 347,215, остаток основного долга кредитов с просрочкой 41 417,000, из него более 180 дней (высокий риск: КЗ-04, 05, 10, 19, 23, КЗ-21 № 19-3/061) 28 575,000; доля 55,2 %. Средняя длительность 1 944 / 13 = 149,5 дн. = ФО-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="165" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Крупнейший заёмщик на конец квартала — ОсОО «Ак-Дан», 5 100 000,00 (два кредита КЗ-01).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>Просрочка на 01.09.2026: 13 кредитов (= ФО-27 за сентябрь: тянулись на 01.09.2026 13) — без КЗ-02 (первый день просрочки 12.09.2026), с КЗ-08 и КЗ-24 (срок уплаты штрафов 31.08.2026); появилась 1 (КЗ-02), не стало 1 (КЗ-08 списан). Просроченная задолженность 9 142,098 = просроченные на 01.10.2026 основная сумма и проценты минус не оплаченный взнос сентября (ФО-54 «по графику», просрочка поровну) по курсу 31.08.2026 + штрафы на 31.08.2026 (ФО-07 «на начало»): КЗ-03 98,373; КЗ-04 1 483,448; КЗ-05 951,012; КЗ-09 38,696; КЗ-10 775,752; КЗ-19 471,820; КЗ-21 № 19-3/061 2 031,826 (22,543 тыс. USD × 87,20 + штрафы 66,088), № 22-3/014 381,300, № 24-3/105 22,657; КЗ-22 701,131 (6,773 тыс. EUR × 101,20 + 15,670); КЗ-23 1 568,414 (16,933 тыс. USD × 87,20 + 91,827); КЗ-24 18,400; КЗ-08 599,269 (по набору). Остаток кредитов с просрочкой 40 189,600, из него более 180 дней 16 598,000 (КЗ-04 182 дн., КЗ-05 379, КЗ-08 498, КЗ-10 230, КЗ-23 215; КЗ-19 и КЗ-21 № 19-3/061 — 160); доля 53,1 %; средняя длительность 2 062 / 13 = 158,6 дн.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Реструктурированных кредитов на конец квартала 1 (КЗ-06, № 20-2/090, 1 800 000,00); кредитов, остаток которых больше оценки залога, — 1 (КЗ-19: остаток 2 200 000,00, оценка 1 800 000,00 по ФО-57).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>Группы — как ФО-24: на 31.08.2026 1.1 — 33 598,400, 1.2 — 35 439,600, 2.1–2.3 — 6 600,000; на 30.09.2026 1.1 — 31 820,500, 1.2 — 13 242,000, 2.1–2.3 — 27 775,000, 3.1–3.2 — 2 200,000, 4 — 0,00. Проблемных 42 039,600 → 43 217,000 (= ФО-28), заёмщиков 11 → 12; доля 55,6 % → 57,6 % (= ФО-28). Группа 1.1 + проблемные = остаток основного долга на каждую дату.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>6.</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Значение „на начало“ равно значению „на конец“ отчёта за предыдущий квартал.</t>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>Концентрация: крупнейший заёмщик на обе даты — ОсОО «Кемин-Курулуш» (3 кредита), 15 464,000 → 15 500,000, доля 20,4 % → 20,7 %. Пятёрка на конец — КЗ-21, КЗ-23, КЗ-25, КЗ-01, КЗ-22: 40 655,000, 54,2 %; на начало пятёрка другая — вместо КЗ-22 (4 857,600) ОсОО «Кут-Мүлк» (5 232,000): 41 160,400, 54,4 %. Валютные — по курсу своей даты, как ФО-24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="120" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>Обеспеченность — по правилу вида «Обеспеченность кредитов залогом» ФО-14. На 30.09.2026: КЗ-04 — обеспечен (3 600,000, залоговая 7 700,000, порог 120 %); КЗ-14 — не обеспечен, недостаёт 515,000 (= ФО-14, вид, и ФО-61); КЗ-20 — не обеспечен: 1 100,000 × 120 % = 1 320,000 против залоговой 1 050,000, недостаёт 270,000 (договор залога № 25-3/014-З1 в наборе есть, в образце вида ФО-14 кредита нет); всего 7 650,000, недостаёт 785,000. На 31.08.2026: КЗ-04; КЗ-14 — залоговая 4 610,000 (трактор утрачен 12.09.2026) против 4 500,000 — обеспечен; КЗ-15 — 500,000, залоговая 3 800,000; КЗ-20 — 1 150,000, недостаёт 330,000; всего 8 250,000. Кредиты без залога — остаток основного долга минус кредиты с залогом: 67 388,000 → 67 387,500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>Реструктуризация: реструктурированных 0 → 1 — КЗ-06 № 20-2/090, дополнительное соглашение № 2 от 08.09.2026, остаток 1 800,000 (= ФО-57); обращений в работе 2 → 2: на 31.08.2026 КЗ-06 и КЗ-13, на 30.09.2026 КЗ-02 и КЗ-13 (= ФО-10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>Строка выше = сумма строк «в том числе» в каждой колонке, где они заполнены. Значение «на начало» равно значению «на конец» отчёта за предыдущий период того же вида.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="26">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
